--- a/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:20</t>
+    <t xml:space="preserve">2026-09-10 01:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:34</t>
+    <t xml:space="preserve">2026-09-12 22:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:45</t>
+    <t xml:space="preserve">2026-09-24 00:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:13</t>
+    <t xml:space="preserve">2026-10-02 15:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:59</t>
+    <t xml:space="preserve">2026-10-04 10:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2024_o higgins.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:46</t>
+    <t xml:space="preserve">2026-10-05 16:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
